--- a/artfynd/A 39168-2026 artfynd.xlsx
+++ b/artfynd/A 39168-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -879,6 +879,577 @@
       <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/130210053</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137271467</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93483</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Röbykärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>686799</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6618886</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Två fruktkroppar.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137271467</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137271571</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58020</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Röbykärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>686892</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6618929</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hackmärken på torraka. På samma torraka även gnagspår av mindre märgborre.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137271571</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137271610</v>
+      </c>
+      <c r="B6" t="n">
+        <v>8464</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Röbykärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>686892</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6618929</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gnagspår på torraka. På samma torraka även hackmärken efter spillkråka.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137271610</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137271649</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99394</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Röbykärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>687071</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6618963</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>En planta.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137271649</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137271688</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99394</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Röbykärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>687070</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6618964</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ca 14 plantor.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137271688</t>
         </is>
       </c>
     </row>
@@ -886,6 +1457,11 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39168-2026 artfynd.xlsx
+++ b/artfynd/A 39168-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137271467</v>
       </c>
       <c r="B4" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137271571</v>
       </c>
       <c r="B5" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>137271610</v>
       </c>
       <c r="B6" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>137271649</v>
       </c>
       <c r="B7" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>137271688</v>
       </c>
       <c r="B8" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 39168-2026 artfynd.xlsx
+++ b/artfynd/A 39168-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137271467</v>
       </c>
       <c r="B4" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>137271649</v>
       </c>
       <c r="B7" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>137271688</v>
       </c>
       <c r="B8" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 39168-2026 artfynd.xlsx
+++ b/artfynd/A 39168-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,38 +999,41 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137271571</v>
+        <v>137339318</v>
       </c>
       <c r="B5" t="n">
-        <v>58030</v>
+        <v>93494</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1038,13 +1041,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>686892</v>
+        <v>686788</v>
       </c>
       <c r="R5" t="n">
-        <v>6618929</v>
+        <v>6618880</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,14 +1074,19 @@
           <t>2026-10-15</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hackmärken på torraka. På samma torraka även gnagspår av mindre märgborre.</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,33 +1095,34 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Gustav Bringby</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Gustav Bringby</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271571</t>
+          <t>https://artportalen.se/Sighting/137339318</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137271610</v>
+        <v>137271571</v>
       </c>
       <c r="B6" t="n">
-        <v>8470</v>
+        <v>58030</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1121,25 +1130,24 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
@@ -1190,7 +1198,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Gnagspår på torraka. På samma torraka även hackmärken efter spillkråka.</t>
+          <t>Hackmärken på torraka. På samma torraka även gnagspår av mindre märgborre.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1199,7 +1207,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1217,48 +1224,45 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271610</t>
+          <t>https://artportalen.se/Sighting/137271571</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137271649</v>
+        <v>137271610</v>
       </c>
       <c r="B7" t="n">
-        <v>99405</v>
+        <v>8470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1266,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>687071</v>
+        <v>686892</v>
       </c>
       <c r="R7" t="n">
-        <v>6618963</v>
+        <v>6618929</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,7 +1310,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>En planta.</t>
+          <t>Gnagspår på torraka. På samma torraka även hackmärken efter spillkråka.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1333,13 +1337,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271649</t>
+          <t>https://artportalen.se/Sighting/137271610</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137271688</v>
+        <v>137271649</v>
       </c>
       <c r="B8" t="n">
         <v>99405</v>
@@ -1369,7 +1373,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -1382,10 +1386,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687070</v>
+        <v>687071</v>
       </c>
       <c r="R8" t="n">
-        <v>6618964</v>
+        <v>6618963</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1426,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ca 14 plantor.</t>
+          <t>En planta.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,6 +1452,122 @@
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137271649</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137271688</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99405</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Röbykärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>687070</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6618964</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ca 14 plantor.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137271688</t>
         </is>
@@ -1462,6 +1582,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39168-2026 artfynd.xlsx
+++ b/artfynd/A 39168-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137271467</v>
       </c>
       <c r="B4" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137339318</v>
       </c>
       <c r="B5" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>137271571</v>
       </c>
       <c r="B6" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>137271649</v>
       </c>
       <c r="B8" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>137271688</v>
       </c>
       <c r="B9" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 39168-2026 artfynd.xlsx
+++ b/artfynd/A 39168-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137271467</v>
       </c>
       <c r="B4" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137339318</v>
       </c>
       <c r="B5" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>137271649</v>
       </c>
       <c r="B8" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>137271688</v>
       </c>
       <c r="B9" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 39168-2026 artfynd.xlsx
+++ b/artfynd/A 39168-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137271467</v>
       </c>
       <c r="B4" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137339318</v>
       </c>
       <c r="B5" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>137271571</v>
       </c>
       <c r="B6" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>137271649</v>
       </c>
       <c r="B8" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>137271688</v>
       </c>
       <c r="B9" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 39168-2026 artfynd.xlsx
+++ b/artfynd/A 39168-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130210043</v>
+        <v>137427498</v>
       </c>
       <c r="B2" t="n">
-        <v>91909</v>
+        <v>92452</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kårsta, Upl</t>
+          <t>Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>686839</v>
+        <v>687042</v>
       </c>
       <c r="R2" t="n">
-        <v>6619021</v>
+        <v>6618970</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,65 +774,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Kalle Skarin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Kalle Skarin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130210043</t>
+          <t>https://artportalen.se/Sighting/137427498</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130210053</v>
+        <v>137433295</v>
       </c>
       <c r="B3" t="n">
-        <v>97231</v>
+        <v>92452</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2869</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kårsta, Upl</t>
+          <t>Tjusta, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>686883</v>
+        <v>687047</v>
       </c>
       <c r="R3" t="n">
-        <v>6619066</v>
+        <v>6618959</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +856,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,69 +886,69 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130210053</t>
+          <t>https://artportalen.se/Sighting/137433295</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137271467</v>
+        <v>137433283</v>
       </c>
       <c r="B4" t="n">
-        <v>93507</v>
+        <v>92398</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>1105</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Röbykärret, Upl</t>
+          <t>Tjusta, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>686799</v>
+        <v>686802</v>
       </c>
       <c r="R4" t="n">
-        <v>6618886</v>
+        <v>6618967</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -956,24 +975,29 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Två fruktkroppar.</t>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
@@ -982,27 +1006,31 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271467</t>
+          <t>https://artportalen.se/Sighting/137433283</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137339318</v>
+        <v>130210043</v>
       </c>
       <c r="B5" t="n">
-        <v>93507</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1010,44 +1038,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Röbykärret, Upl</t>
+          <t>Kårsta, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>686788</v>
+        <v>686839</v>
       </c>
       <c r="R5" t="n">
-        <v>6618880</v>
+        <v>6619021</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,22 +1092,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:19</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:19</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1095,76 +1106,71 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Gustav Bringby</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Gustav Bringby</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137339318</t>
+          <t>https://artportalen.se/Sighting/130210043</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137271571</v>
+        <v>137433281</v>
       </c>
       <c r="B6" t="n">
-        <v>58032</v>
+        <v>92181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Röbykärret, Upl</t>
+          <t>Tjusta, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>686892</v>
+        <v>686841</v>
       </c>
       <c r="R6" t="n">
-        <v>6618929</v>
+        <v>6619009</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1188,17 +1194,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hackmärken på torraka. På samma torraka även gnagspår av mindre märgborre.</t>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,27 +1224,31 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271571</t>
+          <t>https://artportalen.se/Sighting/137433281</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137271610</v>
+        <v>137433280</v>
       </c>
       <c r="B7" t="n">
-        <v>8470</v>
+        <v>96642</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,39 +1256,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>2812</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Röbykärret, Upl</t>
+          <t>Tjusta, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>686892</v>
+        <v>686772</v>
       </c>
       <c r="R7" t="n">
-        <v>6618929</v>
+        <v>6618995</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,17 +1310,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gnagspår på torraka. På samma torraka även hackmärken efter spillkråka.</t>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1319,80 +1334,75 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271610</t>
+          <t>https://artportalen.se/Sighting/137433280</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137271649</v>
+        <v>130210053</v>
       </c>
       <c r="B8" t="n">
-        <v>99418</v>
+        <v>97231</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Röbykärret, Upl</t>
+          <t>Kårsta, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>687071</v>
+        <v>686883</v>
       </c>
       <c r="R8" t="n">
-        <v>6618963</v>
+        <v>6619066</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1416,17 +1426,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>En planta.</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1435,77 +1440,68 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271649</t>
+          <t>https://artportalen.se/Sighting/130210053</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137271688</v>
+        <v>137428864</v>
       </c>
       <c r="B9" t="n">
-        <v>99418</v>
+        <v>93517</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Röbykärret, Upl</t>
+          <t>Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>687070</v>
+        <v>687089</v>
       </c>
       <c r="R9" t="n">
-        <v>6618964</v>
+        <v>6618970</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,17 +1528,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ca 14 plantor.</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,25 +1542,3228 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Kalle Skarin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Kalle Skarin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137428864</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137271467</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93519</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Röbykärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>686799</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6618886</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Två fruktkroppar.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137271467</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137339318</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93519</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Röbykärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>686788</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6618880</v>
+      </c>
+      <c r="S11" t="n">
+        <v>9</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137339318</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137433289</v>
+      </c>
+      <c r="B12" t="n">
+        <v>93519</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tjusta, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>686866</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6618919</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433289</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137426876</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80151</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Norrdal, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>686879</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6618906</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kalle Skarin</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kalle Skarin</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137426876</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137433287</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80151</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Tjusta, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>686846</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6618925</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433287</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137433298</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80151</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Tjusta, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>686984</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6618969</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433298</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137433301</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57956</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100001</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Duvhök</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Astur gentilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Tjusta, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>686822</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6619053</v>
+      </c>
+      <c r="S16" t="n">
+        <v>9</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433301</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137271571</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58032</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Röbykärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>686892</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6618929</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Hackmärken på torraka. På samma torraka även gnagspår av mindre märgborre.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137271571</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137433276</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58032</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Tjusta, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>686751</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6618990</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433276</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137433278</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58032</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Tjusta, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>686767</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6618966</v>
+      </c>
+      <c r="S19" t="n">
+        <v>12</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433278</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137433279</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58032</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Tjusta, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>686772</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6618991</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433279</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137433288</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58032</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Tjusta, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>686885</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6618932</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433288</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137433291</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58032</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Tjusta, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>686912</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6618976</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433291</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137433294</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58032</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Tjusta, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>687051</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6618967</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433294</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>137433297</v>
+      </c>
+      <c r="B24" t="n">
+        <v>4783</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Tjusta, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>687069</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6618943</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433297</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137433282</v>
+      </c>
+      <c r="B25" t="n">
+        <v>5208</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Tjusta, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>686840</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6619015</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433282</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>137433293</v>
+      </c>
+      <c r="B26" t="n">
+        <v>5208</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Tjusta, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>687050</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6618936</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433293</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>137271610</v>
+      </c>
+      <c r="B27" t="n">
+        <v>8470</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Röbykärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>686892</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6618929</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Gnagspår på torraka. På samma torraka även hackmärken efter spillkråka.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137271610</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>137428120</v>
+      </c>
+      <c r="B28" t="n">
+        <v>8470</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Stormossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>687136</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6619015</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kalle Skarin</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kalle Skarin</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137428120</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>137433284</v>
+      </c>
+      <c r="B29" t="n">
+        <v>8470</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Tjusta, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>686803</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6618948</v>
+      </c>
+      <c r="S29" t="n">
+        <v>11</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433284</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>137433286</v>
+      </c>
+      <c r="B30" t="n">
+        <v>8459</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Tjusta, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>686825</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6618935</v>
+      </c>
+      <c r="S30" t="n">
+        <v>11</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433286</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>137433290</v>
+      </c>
+      <c r="B31" t="n">
+        <v>8459</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Tjusta, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>686896</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6618974</v>
+      </c>
+      <c r="S31" t="n">
+        <v>11</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433290</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>137433296</v>
+      </c>
+      <c r="B32" t="n">
+        <v>8459</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Tjusta, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>687119</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6618976</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433296</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>137271649</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99430</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Röbykärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>687071</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6618963</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>En planta.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137271649</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>137271688</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99430</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Röbykärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>687070</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6618964</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ca 14 plantor.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/137271688</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>137433299</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99430</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Tjusta, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>686926</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6619002</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433299</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>137433300</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99430</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Tjusta, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>686820</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6619042</v>
+      </c>
+      <c r="S36" t="n">
+        <v>11</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>4 vinterståndare</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433300</t>
         </is>
       </c>
     </row>
@@ -1583,6 +4777,33 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39168-2026 artfynd.xlsx
+++ b/artfynd/A 39168-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137427498</v>
       </c>
       <c r="B2" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137433295</v>
       </c>
       <c r="B3" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,51 +907,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137433283</v>
+        <v>130210043</v>
       </c>
       <c r="B4" t="n">
-        <v>92398</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1105</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjusta, Upl</t>
+          <t>Kårsta, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>686802</v>
+        <v>686839</v>
       </c>
       <c r="R4" t="n">
-        <v>6618967</v>
+        <v>6619021</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,62 +972,47 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:20</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:20</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Vallentuna skogsgrupp</t>
-        </is>
-      </c>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433283</t>
+          <t>https://artportalen.se/Sighting/130210043</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130210043</v>
+        <v>137433281</v>
       </c>
       <c r="B5" t="n">
-        <v>91909</v>
+        <v>92182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1058,17 +1040,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kårsta, Upl</t>
+          <t>Tjusta, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>686839</v>
+        <v>686841</v>
       </c>
       <c r="R5" t="n">
-        <v>6619021</v>
+        <v>6619009</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,12 +1074,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,49 +1104,53 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130210043</t>
+          <t>https://artportalen.se/Sighting/137433281</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137433281</v>
+        <v>137433280</v>
       </c>
       <c r="B6" t="n">
-        <v>92181</v>
+        <v>96643</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>2812</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1164,13 +1160,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>686841</v>
+        <v>686772</v>
       </c>
       <c r="R6" t="n">
-        <v>6619009</v>
+        <v>6618995</v>
       </c>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1199,7 +1195,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1209,7 +1205,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,16 +1235,16 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433281</t>
+          <t>https://artportalen.se/Sighting/137433280</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137433280</v>
+        <v>130210053</v>
       </c>
       <c r="B7" t="n">
-        <v>96642</v>
+        <v>97231</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,37 +1252,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2812</v>
+        <v>2869</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tjusta, Upl</t>
+          <t>Kårsta, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>686772</v>
+        <v>686883</v>
       </c>
       <c r="R7" t="n">
-        <v>6618995</v>
+        <v>6619066</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,22 +1306,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:57</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:57</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,69 +1326,65 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Vallentuna skogsgrupp</t>
-        </is>
-      </c>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433280</t>
+          <t>https://artportalen.se/Sighting/130210053</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130210053</v>
+        <v>137428864</v>
       </c>
       <c r="B8" t="n">
-        <v>97231</v>
+        <v>93518</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2869</v>
+        <v>5964</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kårsta, Upl</t>
+          <t>Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>686883</v>
+        <v>687089</v>
       </c>
       <c r="R8" t="n">
-        <v>6619066</v>
+        <v>6618970</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,12 +1408,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1446,27 +1428,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Kalle Skarin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Kalle Skarin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130210053</t>
+          <t>https://artportalen.se/Sighting/137428864</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137428864</v>
+        <v>137271467</v>
       </c>
       <c r="B9" t="n">
-        <v>93517</v>
+        <v>93520</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,34 +1456,41 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5964</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stormossen, Upl</t>
+          <t>Röbykärret, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>687089</v>
+        <v>686799</v>
       </c>
       <c r="R9" t="n">
-        <v>6618970</v>
+        <v>6618886</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,12 +1517,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Två fruktkroppar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1542,33 +1536,34 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kalle Skarin</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kalle Skarin</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137428864</t>
+          <t>https://artportalen.se/Sighting/137271467</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137271467</v>
+        <v>137339318</v>
       </c>
       <c r="B10" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1593,12 +1588,12 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1607,13 +1602,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>686799</v>
+        <v>686788</v>
       </c>
       <c r="R10" t="n">
-        <v>6618886</v>
+        <v>6618880</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1640,14 +1635,19 @@
           <t>2026-10-15</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Två fruktkroppar.</t>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1663,27 +1663,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Gustav Bringby</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Gustav Bringby</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271467</t>
+          <t>https://artportalen.se/Sighting/137339318</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137339318</v>
+        <v>137433289</v>
       </c>
       <c r="B11" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1709,26 +1709,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Röbykärret, Upl</t>
+          <t>Tjusta, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>686788</v>
+        <v>686866</v>
       </c>
       <c r="R11" t="n">
-        <v>6618880</v>
+        <v>6618919</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1752,22 +1745,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1776,34 +1769,37 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Gustav Bringby</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Gustav Bringby</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137339318</t>
+          <t>https://artportalen.se/Sighting/137433289</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137433289</v>
+        <v>137426876</v>
       </c>
       <c r="B12" t="n">
-        <v>93519</v>
+        <v>80152</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,34 +1807,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tjusta, Upl</t>
+          <t>Norrdal, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>686866</v>
+        <v>686879</v>
       </c>
       <c r="R12" t="n">
-        <v>6618919</v>
+        <v>6618906</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,19 +1864,9 @@
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>12:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,31 +1881,27 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Kalle Skarin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Vallentuna skogsgrupp</t>
-        </is>
-      </c>
+          <t>Kalle Skarin</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433289</t>
+          <t>https://artportalen.se/Sighting/137426876</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137426876</v>
+        <v>137433287</v>
       </c>
       <c r="B13" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,14 +1929,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Norrdal, Upl</t>
+          <t>Tjusta, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>686879</v>
+        <v>686846</v>
       </c>
       <c r="R13" t="n">
-        <v>6618906</v>
+        <v>6618925</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1984,9 +1966,19 @@
           <t>2026-10-24</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2001,27 +1993,31 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kalle Skarin</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kalle Skarin</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137426876</t>
+          <t>https://artportalen.se/Sighting/137433287</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137433287</v>
+        <v>137433298</v>
       </c>
       <c r="B14" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2053,10 +2049,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>686846</v>
+        <v>686984</v>
       </c>
       <c r="R14" t="n">
-        <v>6618925</v>
+        <v>6618969</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2088,7 +2084,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2098,7 +2094,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2128,16 +2124,16 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433287</t>
+          <t>https://artportalen.se/Sighting/137433298</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137433298</v>
+        <v>137433301</v>
       </c>
       <c r="B15" t="n">
-        <v>80151</v>
+        <v>57956</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2145,37 +2141,45 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>100001</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tjusta, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>686984</v>
+        <v>686822</v>
       </c>
       <c r="R15" t="n">
-        <v>6618969</v>
+        <v>6619053</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2204,7 +2208,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2214,7 +2218,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2244,33 +2248,33 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433298</t>
+          <t>https://artportalen.se/Sighting/137433301</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137433301</v>
+        <v>137271571</v>
       </c>
       <c r="B16" t="n">
-        <v>57956</v>
+        <v>58032</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100001</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2278,28 +2282,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Tjusta, Upl</t>
+          <t>Röbykärret, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>686822</v>
+        <v>686892</v>
       </c>
       <c r="R16" t="n">
-        <v>6619053</v>
+        <v>6618929</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2323,22 +2323,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Hackmärken på torraka. På samma torraka även gnagspår av mindre märgborre.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2353,28 +2348,24 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Vallentuna skogsgrupp</t>
-        </is>
-      </c>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433301</t>
+          <t>https://artportalen.se/Sighting/137271571</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137271571</v>
+        <v>137433276</v>
       </c>
       <c r="B17" t="n">
         <v>58032</v>
@@ -2409,14 +2400,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Röbykärret, Upl</t>
+          <t>Tjusta, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>686892</v>
+        <v>686751</v>
       </c>
       <c r="R17" t="n">
-        <v>6618929</v>
+        <v>6618990</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2443,17 +2434,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Hackmärken på torraka. På samma torraka även gnagspår av mindre märgborre.</t>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2468,24 +2464,28 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271571</t>
+          <t>https://artportalen.se/Sighting/137433276</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>137433276</v>
+        <v>137433278</v>
       </c>
       <c r="B18" t="n">
         <v>58032</v>
@@ -2524,13 +2524,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>686751</v>
+        <v>686767</v>
       </c>
       <c r="R18" t="n">
-        <v>6618990</v>
+        <v>6618966</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2599,13 +2599,13 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433276</t>
+          <t>https://artportalen.se/Sighting/137433278</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137433278</v>
+        <v>137433279</v>
       </c>
       <c r="B19" t="n">
         <v>58032</v>
@@ -2644,13 +2644,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>686767</v>
+        <v>686772</v>
       </c>
       <c r="R19" t="n">
-        <v>6618966</v>
+        <v>6618991</v>
       </c>
       <c r="S19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2719,13 +2719,13 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433278</t>
+          <t>https://artportalen.se/Sighting/137433279</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>137433279</v>
+        <v>137433288</v>
       </c>
       <c r="B20" t="n">
         <v>58032</v>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>686772</v>
+        <v>686885</v>
       </c>
       <c r="R20" t="n">
-        <v>6618991</v>
+        <v>6618932</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2839,13 +2839,13 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433279</t>
+          <t>https://artportalen.se/Sighting/137433288</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>137433288</v>
+        <v>137433291</v>
       </c>
       <c r="B21" t="n">
         <v>58032</v>
@@ -2884,10 +2884,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>686885</v>
+        <v>686912</v>
       </c>
       <c r="R21" t="n">
-        <v>6618932</v>
+        <v>6618976</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2959,13 +2959,13 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433288</t>
+          <t>https://artportalen.se/Sighting/137433291</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>137433291</v>
+        <v>137433294</v>
       </c>
       <c r="B22" t="n">
         <v>58032</v>
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>686912</v>
+        <v>687051</v>
       </c>
       <c r="R22" t="n">
-        <v>6618976</v>
+        <v>6618967</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3079,16 +3079,16 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433291</t>
+          <t>https://artportalen.se/Sighting/137433294</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>137433294</v>
+        <v>137433297</v>
       </c>
       <c r="B23" t="n">
-        <v>58032</v>
+        <v>4783</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,24 +3096,25 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
@@ -3124,10 +3125,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>687051</v>
+        <v>687069</v>
       </c>
       <c r="R23" t="n">
-        <v>6618967</v>
+        <v>6618943</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3159,7 +3160,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3169,15 +3170,16 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3199,16 +3201,16 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433294</t>
+          <t>https://artportalen.se/Sighting/137433297</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>137433297</v>
+        <v>137433282</v>
       </c>
       <c r="B24" t="n">
-        <v>4783</v>
+        <v>5208</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3216,21 +3218,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100299</v>
+        <v>105930</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3245,10 +3247,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>687069</v>
+        <v>686840</v>
       </c>
       <c r="R24" t="n">
-        <v>6618943</v>
+        <v>6619015</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3280,7 +3282,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3290,14 +3292,14 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
@@ -3321,13 +3323,13 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433297</t>
+          <t>https://artportalen.se/Sighting/137433282</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>137433282</v>
+        <v>137433293</v>
       </c>
       <c r="B25" t="n">
         <v>5208</v>
@@ -3367,10 +3369,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>686840</v>
+        <v>687050</v>
       </c>
       <c r="R25" t="n">
-        <v>6619015</v>
+        <v>6618936</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3402,7 +3404,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3412,7 +3414,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3443,16 +3445,16 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433282</t>
+          <t>https://artportalen.se/Sighting/137433293</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>137433293</v>
+        <v>137271610</v>
       </c>
       <c r="B26" t="n">
-        <v>5208</v>
+        <v>8470</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3460,21 +3462,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3485,14 +3487,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Tjusta, Upl</t>
+          <t>Röbykärret, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>687050</v>
+        <v>686892</v>
       </c>
       <c r="R26" t="n">
-        <v>6618936</v>
+        <v>6618929</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3519,22 +3521,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>13:12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:12</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Gnagspår på torraka. På samma torraka även hackmärken efter spillkråka.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3550,28 +3547,24 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>Vallentuna skogsgrupp</t>
-        </is>
-      </c>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433293</t>
+          <t>https://artportalen.se/Sighting/137271610</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>137271610</v>
+        <v>137428120</v>
       </c>
       <c r="B27" t="n">
         <v>8470</v>
@@ -3600,24 +3593,19 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Röbykärret, Upl</t>
+          <t>Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>686892</v>
+        <v>687136</v>
       </c>
       <c r="R27" t="n">
-        <v>6618929</v>
+        <v>6619015</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3641,17 +3629,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Gnagspår på torraka. På samma torraka även hackmärken efter spillkråka.</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3660,31 +3643,30 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Kalle Skarin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Kalle Skarin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271610</t>
+          <t>https://artportalen.se/Sighting/137428120</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>137428120</v>
+        <v>137433284</v>
       </c>
       <c r="B28" t="n">
         <v>8470</v>
@@ -3713,19 +3695,24 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stormossen, Upl</t>
+          <t>Tjusta, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>687136</v>
+        <v>686803</v>
       </c>
       <c r="R28" t="n">
-        <v>6619015</v>
+        <v>6618948</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3752,44 +3739,59 @@
           <t>2026-10-24</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kalle Skarin</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kalle Skarin</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137428120</t>
+          <t>https://artportalen.se/Sighting/137433284</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>137433284</v>
+        <v>137433286</v>
       </c>
       <c r="B29" t="n">
-        <v>8470</v>
+        <v>8459</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3797,21 +3799,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3826,10 +3828,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>686803</v>
+        <v>686825</v>
       </c>
       <c r="R29" t="n">
-        <v>6618948</v>
+        <v>6618935</v>
       </c>
       <c r="S29" t="n">
         <v>11</v>
@@ -3861,7 +3863,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3871,7 +3873,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3902,13 +3904,13 @@
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433284</t>
+          <t>https://artportalen.se/Sighting/137433286</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>137433286</v>
+        <v>137433290</v>
       </c>
       <c r="B30" t="n">
         <v>8459</v>
@@ -3948,10 +3950,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>686825</v>
+        <v>686896</v>
       </c>
       <c r="R30" t="n">
-        <v>6618935</v>
+        <v>6618974</v>
       </c>
       <c r="S30" t="n">
         <v>11</v>
@@ -3983,7 +3985,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3993,7 +3995,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4024,13 +4026,13 @@
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433286</t>
+          <t>https://artportalen.se/Sighting/137433290</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>137433290</v>
+        <v>137433296</v>
       </c>
       <c r="B31" t="n">
         <v>8459</v>
@@ -4070,13 +4072,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>686896</v>
+        <v>687119</v>
       </c>
       <c r="R31" t="n">
-        <v>6618974</v>
+        <v>6618976</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4105,7 +4107,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4115,7 +4117,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4146,56 +4148,59 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433290</t>
+          <t>https://artportalen.se/Sighting/137433296</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>137433296</v>
+        <v>137271649</v>
       </c>
       <c r="B32" t="n">
-        <v>8459</v>
+        <v>99431</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Tjusta, Upl</t>
+          <t>Röbykärret, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>687119</v>
+        <v>687071</v>
       </c>
       <c r="R32" t="n">
-        <v>6618976</v>
+        <v>6618963</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4222,22 +4227,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:31</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:31</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>En planta.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4253,31 +4253,27 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Vallentuna skogsgrupp</t>
-        </is>
-      </c>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433296</t>
+          <t>https://artportalen.se/Sighting/137271649</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>137271649</v>
+        <v>137271688</v>
       </c>
       <c r="B33" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4304,7 +4300,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
@@ -4317,10 +4313,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>687071</v>
+        <v>687070</v>
       </c>
       <c r="R33" t="n">
-        <v>6618963</v>
+        <v>6618964</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4357,7 +4353,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>En planta.</t>
+          <t>Ca 14 plantor.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4384,16 +4380,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271649</t>
+          <t>https://artportalen.se/Sighting/137271688</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>137271688</v>
+        <v>137433299</v>
       </c>
       <c r="B34" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4420,23 +4416,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Röbykärret, Upl</t>
+          <t>Tjusta, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>687070</v>
+        <v>686926</v>
       </c>
       <c r="R34" t="n">
-        <v>6618964</v>
+        <v>6619002</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4463,17 +4463,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ca 14 plantor.</t>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4489,27 +4494,31 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271688</t>
+          <t>https://artportalen.se/Sighting/137433299</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>137433299</v>
+        <v>137433300</v>
       </c>
       <c r="B35" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4536,7 +4545,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>350</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4553,13 +4562,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>686926</v>
+        <v>686820</v>
       </c>
       <c r="R35" t="n">
-        <v>6619002</v>
+        <v>6619042</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4588,7 +4597,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4598,7 +4607,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>4 vinterståndare</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4629,52 +4643,43 @@
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433299</t>
+          <t>https://artportalen.se/Sighting/137433300</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>137433300</v>
+        <v>137433283</v>
       </c>
       <c r="B36" t="n">
-        <v>99430</v>
+        <v>92573</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6040162</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallkötticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4682,13 +4687,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>686820</v>
+        <v>686802</v>
       </c>
       <c r="R36" t="n">
-        <v>6619042</v>
+        <v>6618967</v>
       </c>
       <c r="S36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4717,7 +4722,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4727,12 +4732,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:39</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>4 vinterståndare</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433300</t>
+          <t>https://artportalen.se/Sighting/137433283</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 39168-2026 artfynd.xlsx
+++ b/artfynd/A 39168-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ36"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137427498</v>
       </c>
       <c r="B2" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137433295</v>
       </c>
       <c r="B3" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>137433281</v>
       </c>
       <c r="B5" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>137433280</v>
       </c>
       <c r="B6" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>137428864</v>
       </c>
       <c r="B8" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>137271467</v>
       </c>
       <c r="B9" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>137339318</v>
       </c>
       <c r="B10" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>137433289</v>
       </c>
       <c r="B11" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>137426876</v>
       </c>
       <c r="B12" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>137433287</v>
       </c>
       <c r="B13" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>137433298</v>
       </c>
       <c r="B14" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2130,27 +2130,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137433301</v>
+        <v>137271571</v>
       </c>
       <c r="B15" t="n">
-        <v>57956</v>
+        <v>58032</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100001</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2158,28 +2158,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tjusta, Upl</t>
+          <t>Röbykärret, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>686822</v>
+        <v>686892</v>
       </c>
       <c r="R15" t="n">
-        <v>6619053</v>
+        <v>6618929</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2203,22 +2199,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Hackmärken på torraka. På samma torraka även gnagspår av mindre märgborre.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2233,28 +2224,24 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Vallentuna skogsgrupp</t>
-        </is>
-      </c>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433301</t>
+          <t>https://artportalen.se/Sighting/137271571</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137271571</v>
+        <v>137433276</v>
       </c>
       <c r="B16" t="n">
         <v>58032</v>
@@ -2289,14 +2276,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Röbykärret, Upl</t>
+          <t>Tjusta, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>686892</v>
+        <v>686751</v>
       </c>
       <c r="R16" t="n">
-        <v>6618929</v>
+        <v>6618990</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2323,17 +2310,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Hackmärken på torraka. På samma torraka även gnagspår av mindre märgborre.</t>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2348,24 +2340,28 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271571</t>
+          <t>https://artportalen.se/Sighting/137433276</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137433276</v>
+        <v>137433278</v>
       </c>
       <c r="B17" t="n">
         <v>58032</v>
@@ -2404,13 +2400,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>686751</v>
+        <v>686767</v>
       </c>
       <c r="R17" t="n">
-        <v>6618990</v>
+        <v>6618966</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2439,7 +2435,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2449,7 +2445,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2479,13 +2475,13 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433276</t>
+          <t>https://artportalen.se/Sighting/137433278</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>137433278</v>
+        <v>137433279</v>
       </c>
       <c r="B18" t="n">
         <v>58032</v>
@@ -2524,13 +2520,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>686767</v>
+        <v>686772</v>
       </c>
       <c r="R18" t="n">
-        <v>6618966</v>
+        <v>6618991</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2559,7 +2555,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2569,7 +2565,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2599,13 +2595,13 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433278</t>
+          <t>https://artportalen.se/Sighting/137433279</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137433279</v>
+        <v>137433288</v>
       </c>
       <c r="B19" t="n">
         <v>58032</v>
@@ -2644,10 +2640,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>686772</v>
+        <v>686885</v>
       </c>
       <c r="R19" t="n">
-        <v>6618991</v>
+        <v>6618932</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2679,7 +2675,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2689,7 +2685,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2719,13 +2715,13 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433279</t>
+          <t>https://artportalen.se/Sighting/137433288</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>137433288</v>
+        <v>137433291</v>
       </c>
       <c r="B20" t="n">
         <v>58032</v>
@@ -2764,10 +2760,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>686885</v>
+        <v>686912</v>
       </c>
       <c r="R20" t="n">
-        <v>6618932</v>
+        <v>6618976</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2799,7 +2795,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2809,7 +2805,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2839,13 +2835,13 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433288</t>
+          <t>https://artportalen.se/Sighting/137433291</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>137433291</v>
+        <v>137433294</v>
       </c>
       <c r="B21" t="n">
         <v>58032</v>
@@ -2884,10 +2880,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>686912</v>
+        <v>687051</v>
       </c>
       <c r="R21" t="n">
-        <v>6618976</v>
+        <v>6618967</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2919,7 +2915,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2929,7 +2925,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2959,16 +2955,16 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433291</t>
+          <t>https://artportalen.se/Sighting/137433294</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>137433294</v>
+        <v>137433297</v>
       </c>
       <c r="B22" t="n">
-        <v>58032</v>
+        <v>4783</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2976,24 +2972,25 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
@@ -3004,10 +3001,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>687051</v>
+        <v>687069</v>
       </c>
       <c r="R22" t="n">
-        <v>6618967</v>
+        <v>6618943</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3039,7 +3036,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3049,15 +3046,16 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3079,16 +3077,16 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433294</t>
+          <t>https://artportalen.se/Sighting/137433297</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>137433297</v>
+        <v>137433282</v>
       </c>
       <c r="B23" t="n">
-        <v>4783</v>
+        <v>5208</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3096,21 +3094,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100299</v>
+        <v>105930</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3125,10 +3123,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>687069</v>
+        <v>686840</v>
       </c>
       <c r="R23" t="n">
-        <v>6618943</v>
+        <v>6619015</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3160,7 +3158,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3170,14 +3168,14 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
@@ -3201,13 +3199,13 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433297</t>
+          <t>https://artportalen.se/Sighting/137433282</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>137433282</v>
+        <v>137433293</v>
       </c>
       <c r="B24" t="n">
         <v>5208</v>
@@ -3247,10 +3245,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>686840</v>
+        <v>687050</v>
       </c>
       <c r="R24" t="n">
-        <v>6619015</v>
+        <v>6618936</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3282,7 +3280,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3292,7 +3290,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3323,16 +3321,16 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433282</t>
+          <t>https://artportalen.se/Sighting/137433293</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>137433293</v>
+        <v>137271610</v>
       </c>
       <c r="B25" t="n">
-        <v>5208</v>
+        <v>8470</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3340,21 +3338,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3365,14 +3363,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Tjusta, Upl</t>
+          <t>Röbykärret, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>687050</v>
+        <v>686892</v>
       </c>
       <c r="R25" t="n">
-        <v>6618936</v>
+        <v>6618929</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3399,22 +3397,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>13:12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:12</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Gnagspår på torraka. På samma torraka även hackmärken efter spillkråka.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3430,28 +3423,24 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Vallentuna skogsgrupp</t>
-        </is>
-      </c>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433293</t>
+          <t>https://artportalen.se/Sighting/137271610</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>137271610</v>
+        <v>137428120</v>
       </c>
       <c r="B26" t="n">
         <v>8470</v>
@@ -3480,24 +3469,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Röbykärret, Upl</t>
+          <t>Stormossen, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>686892</v>
+        <v>687136</v>
       </c>
       <c r="R26" t="n">
-        <v>6618929</v>
+        <v>6619015</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3521,17 +3505,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Gnagspår på torraka. På samma torraka även hackmärken efter spillkråka.</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3540,31 +3519,30 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Kalle Skarin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Kalle Skarin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271610</t>
+          <t>https://artportalen.se/Sighting/137428120</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>137428120</v>
+        <v>137433284</v>
       </c>
       <c r="B27" t="n">
         <v>8470</v>
@@ -3593,19 +3571,24 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stormossen, Upl</t>
+          <t>Tjusta, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>687136</v>
+        <v>686803</v>
       </c>
       <c r="R27" t="n">
-        <v>6619015</v>
+        <v>6618948</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3632,44 +3615,59 @@
           <t>2026-10-24</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kalle Skarin</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kalle Skarin</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137428120</t>
+          <t>https://artportalen.se/Sighting/137433284</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>137433284</v>
+        <v>137433286</v>
       </c>
       <c r="B28" t="n">
-        <v>8470</v>
+        <v>8459</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3677,21 +3675,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3706,10 +3704,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>686803</v>
+        <v>686825</v>
       </c>
       <c r="R28" t="n">
-        <v>6618948</v>
+        <v>6618935</v>
       </c>
       <c r="S28" t="n">
         <v>11</v>
@@ -3741,7 +3739,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3751,7 +3749,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3782,13 +3780,13 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433284</t>
+          <t>https://artportalen.se/Sighting/137433286</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>137433286</v>
+        <v>137433290</v>
       </c>
       <c r="B29" t="n">
         <v>8459</v>
@@ -3828,10 +3826,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>686825</v>
+        <v>686896</v>
       </c>
       <c r="R29" t="n">
-        <v>6618935</v>
+        <v>6618974</v>
       </c>
       <c r="S29" t="n">
         <v>11</v>
@@ -3863,7 +3861,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3873,7 +3871,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3904,13 +3902,13 @@
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433286</t>
+          <t>https://artportalen.se/Sighting/137433290</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>137433290</v>
+        <v>137433296</v>
       </c>
       <c r="B30" t="n">
         <v>8459</v>
@@ -3950,13 +3948,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>686896</v>
+        <v>687119</v>
       </c>
       <c r="R30" t="n">
-        <v>6618974</v>
+        <v>6618976</v>
       </c>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3985,7 +3983,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3995,7 +3993,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4026,56 +4024,59 @@
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433290</t>
+          <t>https://artportalen.se/Sighting/137433296</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>137433296</v>
+        <v>137271649</v>
       </c>
       <c r="B31" t="n">
-        <v>8459</v>
+        <v>99434</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Tjusta, Upl</t>
+          <t>Röbykärret, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>687119</v>
+        <v>687071</v>
       </c>
       <c r="R31" t="n">
-        <v>6618976</v>
+        <v>6618963</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4102,22 +4103,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:31</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:31</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>En planta.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4133,31 +4129,27 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Vallentuna skogsgrupp</t>
-        </is>
-      </c>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433296</t>
+          <t>https://artportalen.se/Sighting/137271649</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>137271649</v>
+        <v>137271688</v>
       </c>
       <c r="B32" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4184,7 +4176,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
@@ -4197,10 +4189,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>687071</v>
+        <v>687070</v>
       </c>
       <c r="R32" t="n">
-        <v>6618963</v>
+        <v>6618964</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4237,7 +4229,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>En planta.</t>
+          <t>Ca 14 plantor.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4264,16 +4256,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271649</t>
+          <t>https://artportalen.se/Sighting/137271688</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>137271688</v>
+        <v>137433299</v>
       </c>
       <c r="B33" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4300,23 +4292,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Röbykärret, Upl</t>
+          <t>Tjusta, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>687070</v>
+        <v>686926</v>
       </c>
       <c r="R33" t="n">
-        <v>6618964</v>
+        <v>6619002</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4343,17 +4339,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ca 14 plantor.</t>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4369,27 +4370,31 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271688</t>
+          <t>https://artportalen.se/Sighting/137433299</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>137433299</v>
+        <v>137433300</v>
       </c>
       <c r="B34" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4416,7 +4421,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>350</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4433,13 +4438,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>686926</v>
+        <v>686820</v>
       </c>
       <c r="R34" t="n">
-        <v>6619002</v>
+        <v>6619042</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4468,7 +4473,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4478,7 +4483,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>4 vinterståndare</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4509,52 +4519,43 @@
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433299</t>
+          <t>https://artportalen.se/Sighting/137433300</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>137433300</v>
+        <v>137433283</v>
       </c>
       <c r="B35" t="n">
-        <v>99431</v>
+        <v>92576</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6040162</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallkötticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4562,13 +4563,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>686820</v>
+        <v>686802</v>
       </c>
       <c r="R35" t="n">
-        <v>6619042</v>
+        <v>6618967</v>
       </c>
       <c r="S35" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4597,7 +4598,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4607,12 +4608,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:39</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>4 vinterståndare</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4642,126 +4638,6 @@
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137433300</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>137433283</v>
-      </c>
-      <c r="B36" t="n">
-        <v>92573</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>6040162</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Tallkötticka</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Leptoporus erubescens</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Tjusta, Upl</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>686802</v>
-      </c>
-      <c r="R36" t="n">
-        <v>6618967</v>
-      </c>
-      <c r="S36" t="n">
-        <v>10</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Vallentuna</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Kårsta</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="inlineStr"/>
-      <c r="AG36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Vallentuna skogsgrupp</t>
-        </is>
-      </c>
-      <c r="AZ36" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137433283</t>
         </is>
@@ -4803,7 +4679,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39168-2026 artfynd.xlsx
+++ b/artfynd/A 39168-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137427498</v>
       </c>
       <c r="B2" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137433295</v>
       </c>
       <c r="B3" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>137433281</v>
       </c>
       <c r="B5" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>137433280</v>
       </c>
       <c r="B6" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>137428864</v>
       </c>
       <c r="B8" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>137271467</v>
       </c>
       <c r="B9" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>137339318</v>
       </c>
       <c r="B10" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>137433289</v>
       </c>
       <c r="B11" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>137426876</v>
       </c>
       <c r="B12" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>137433287</v>
       </c>
       <c r="B13" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>137433298</v>
       </c>
       <c r="B14" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>137271571</v>
       </c>
       <c r="B15" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>137433276</v>
       </c>
       <c r="B16" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>137433278</v>
       </c>
       <c r="B17" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>137433279</v>
       </c>
       <c r="B18" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>137433288</v>
       </c>
       <c r="B19" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>137433291</v>
       </c>
       <c r="B20" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>137433294</v>
       </c>
       <c r="B21" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>137271649</v>
       </c>
       <c r="B31" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>137271688</v>
       </c>
       <c r="B32" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>137433299</v>
       </c>
       <c r="B33" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>137433300</v>
       </c>
       <c r="B34" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>137433283</v>
       </c>
       <c r="B35" t="n">
-        <v>92576</v>
+        <v>92580</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
